--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MLDesignAl\TheFinal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D585CE0-70DB-4859-8D1C-38E2ED266E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9144FADD-F760-4614-82F2-D606562FE012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31395" yWindow="255" windowWidth="25530" windowHeight="14415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="23">
   <si>
     <t>模型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -123,7 +123,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +148,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -182,7 +188,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -200,6 +206,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -483,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="18.44140625" customWidth="1"/>
@@ -496,7 +508,7 @@
     <col min="27" max="27" width="28.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>16</v>
       </c>
@@ -539,7 +551,7 @@
       <c r="Z1" s="6"/>
       <c r="AA1" s="6"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -610,7 +622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -640,8 +652,12 @@
       <c r="M3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
+      <c r="N3" s="2">
+        <v>0.6472</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.1865</v>
+      </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="1" t="s">
         <v>1</v>
@@ -661,7 +677,7 @@
       <c r="Z3" s="2"/>
       <c r="AA3" s="2"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -728,7 +744,7 @@
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -758,8 +774,12 @@
       <c r="M5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
+      <c r="N5" s="2">
+        <v>0.64259999999999995</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0.18060000000000001</v>
+      </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="1" t="s">
         <v>3</v>
@@ -779,7 +799,7 @@
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -813,10 +833,10 @@
       <c r="M6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="8">
         <v>0.8397</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="8">
         <v>9.74E-2</v>
       </c>
       <c r="P6" s="5"/>
@@ -850,7 +870,7 @@
         <v>8.9300000000000004E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -921,7 +941,7 @@
         <v>9.3100000000000002E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -992,13 +1012,22 @@
         <v>9.9099999999999994E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="1"/>
+      <c r="M9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0.90149999999999997</v>
+      </c>
+      <c r="O9" s="8">
+        <v>7.8E-2</v>
+      </c>
       <c r="U9" s="3" t="s">
         <v>14</v>
       </c>
@@ -1019,7 +1048,7 @@
         <v>7.2099999999999997E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1030,6 +1059,15 @@
         <v>0.15970000000000001</v>
       </c>
       <c r="D10" s="4"/>
+      <c r="M10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0.8982</v>
+      </c>
+      <c r="O10" s="2">
+        <v>7.9200000000000007E-2</v>
+      </c>
       <c r="U10" s="3" t="s">
         <v>15</v>
       </c>
@@ -1050,7 +1088,7 @@
         <v>7.6899999999999996E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
@@ -1062,7 +1100,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>18</v>
       </c>
@@ -1081,7 +1119,7 @@
       <c r="V13" s="6"/>
       <c r="W13" s="6"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -1111,8 +1149,23 @@
       <c r="W14" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="Y14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
@@ -1135,8 +1188,23 @@
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
       <c r="X15" s="1"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="Y15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>0.87609999999999999</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>9.8799999999999999E-2</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>0.8982</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>8.9300000000000004E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>2</v>
       </c>
@@ -1167,8 +1235,23 @@
         <v>0.88490000000000002</v>
       </c>
       <c r="X16" s="1"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>0.10249999999999999</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>0.88849999999999996</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>9.3100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>3</v>
       </c>
@@ -1199,8 +1282,23 @@
         <v>0.52410000000000001</v>
       </c>
       <c r="X17" s="2"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>0.85570000000000002</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0.11020000000000001</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>0.87439999999999996</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>9.9099999999999994E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1231,8 +1329,23 @@
         <v>0.34460000000000002</v>
       </c>
       <c r="X18" s="2"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>0.90959999999999996</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>8.09E-2</v>
+      </c>
+      <c r="AB18" s="5">
+        <v>0.93069999999999997</v>
+      </c>
+      <c r="AC18" s="5">
+        <v>7.2099999999999997E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>5</v>
       </c>
@@ -1263,8 +1376,23 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="X19" s="2"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>0.90129999999999999</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>8.5500000000000007E-2</v>
+      </c>
+      <c r="AB19" s="2">
+        <v>0.92349999999999999</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>7.6899999999999996E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>6</v>
       </c>
@@ -1296,7 +1424,7 @@
       </c>
       <c r="X20" s="2"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>14</v>
       </c>
@@ -1328,7 +1456,7 @@
       </c>
       <c r="X21" s="2"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>15</v>
       </c>
@@ -1360,10 +1488,10 @@
       </c>
       <c r="X22" s="2"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="X23" s="2"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="M24" s="6" t="s">
         <v>22</v>
       </c>
@@ -1371,7 +1499,7 @@
       <c r="O24" s="6"/>
       <c r="X24" s="2"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="M25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1382,28 +1510,28 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="M26" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="M27" s="1" t="s">
         <v>2</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="M28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
@@ -1414,21 +1542,21 @@
         <v>7.1400000000000005E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="M30" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="M31" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="M32" s="3" t="s">
         <v>14</v>
       </c>
@@ -1448,6 +1576,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="Y1:AA1"/>
     <mergeCell ref="A1:C1"/>
@@ -1455,11 +1588,6 @@
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="U13:W13"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A13:C13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
